--- a/ซ้อมย่อย2.xlsx
+++ b/ซ้อมย่อย2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Test01-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3A645E7-59F9-4A6C-B6EF-65D636F4AD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81FA328-7A2E-4B94-81B9-C6FA22355782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7C1F9745-ADF4-4E4C-9D44-587E8B9044AE}"/>
   </bookViews>
